--- a/backtest_runs/20260410_193731/by_symbol/TSPL/TSPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TSPL/TSPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1958.579999999997</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98041.42</v>
@@ -633,7 +633,7 @@
         <v>-2393.819999999987</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>97606.18000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>97606.18000000001</v>
@@ -771,7 +771,7 @@
         <v>-108.8099999999977</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>97497.37000000001</v>
@@ -817,7 +817,7 @@
         <v>-5222.880000000005</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>92274.49000000001</v>
@@ -955,7 +955,7 @@
         <v>-11316.23999999999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>102720.25</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>102720.25</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>102720.25</v>
@@ -1093,7 +1093,7 @@
         <v>-3046.679999999993</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>99673.57000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-5984.550000000007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>94668.31000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-5766.930000000012</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>107507.89</v>
@@ -1461,7 +1461,7 @@
         <v>-6963.840000000007</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>100544.05</v>
@@ -1507,7 +1507,7 @@
         <v>-2176.199999999992</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>98367.85000000002</v>
@@ -1645,7 +1645,7 @@
         <v>-2937.869999999995</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>95429.98000000003</v>
